--- a/Source data/Source Data Figure S4.xlsx
+++ b/Source data/Source Data Figure S4.xlsx
@@ -3,16 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20337"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{7775BA96-C1AE-48AD-B7D0-D8532405D1E8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{437B7C52-A5ED-4F13-A311-610201F55DA7}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{7775BA96-C1AE-48AD-B7D0-D8532405D1E8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{1C43FB65-9198-4CAE-B5DF-BA3F9C96789C}"/>
   <bookViews>
     <workbookView xWindow="8880" yWindow="732" windowWidth="20520" windowHeight="17148" tabRatio="787" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Figure S4c" sheetId="46" r:id="rId1"/>
-    <sheet name="Figure S4h" sheetId="47" r:id="rId2"/>
+    <sheet name="Figure S4c" sheetId="48" r:id="rId1"/>
+    <sheet name="Figure S4d" sheetId="46" r:id="rId2"/>
+    <sheet name="Figure S4g" sheetId="47" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Figure S4c'!$A$3:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Figure S4d'!$A$3:$G$48</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="81">
   <si>
     <t>CM01</t>
   </si>
@@ -260,7 +261,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CellChat cell-cell interaction counts based on scRNA-seq.</t>
+    <t>The cell-cell interaction counts based on scRNA-seq.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leiden</t>
+  </si>
+  <si>
+    <t>Adipose</t>
+  </si>
+  <si>
+    <t>Intestine</t>
+  </si>
+  <si>
+    <t>Liver</t>
+  </si>
+  <si>
+    <t>Muscle</t>
+  </si>
+  <si>
+    <t>The cell-type composition across the Leiden group.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -339,7 +359,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -368,6 +388,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -650,6 +673,816 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A23586B-2231-4335-B078-8592D133B59F}">
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1">
+        <v>474</v>
+      </c>
+      <c r="C4" s="1">
+        <v>72493</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1999</v>
+      </c>
+      <c r="E4" s="1">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1">
+        <v>99</v>
+      </c>
+      <c r="C5" s="1">
+        <v>72196</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2519</v>
+      </c>
+      <c r="E5" s="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1">
+        <v>438</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D6" s="1">
+        <v>14940</v>
+      </c>
+      <c r="E6" s="1">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1">
+        <v>219</v>
+      </c>
+      <c r="C7" s="1">
+        <v>47861</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2091</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="1">
+        <v>42</v>
+      </c>
+      <c r="C8" s="1">
+        <v>35198</v>
+      </c>
+      <c r="D8" s="1">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="1">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1">
+        <v>35459</v>
+      </c>
+      <c r="D9" s="1">
+        <v>11</v>
+      </c>
+      <c r="E9" s="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="1">
+        <v>102</v>
+      </c>
+      <c r="C10" s="1">
+        <v>19604</v>
+      </c>
+      <c r="D10" s="1">
+        <v>11836</v>
+      </c>
+      <c r="E10" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="1">
+        <v>9814</v>
+      </c>
+      <c r="C11" s="1">
+        <v>11887</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1517</v>
+      </c>
+      <c r="E11" s="1">
+        <v>5273</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="1">
+        <v>365</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18238</v>
+      </c>
+      <c r="D12" s="1">
+        <v>177</v>
+      </c>
+      <c r="E12" s="1">
+        <v>7226</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="1">
+        <v>180</v>
+      </c>
+      <c r="C13" s="1">
+        <v>501</v>
+      </c>
+      <c r="D13" s="1">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1">
+        <v>24231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>170</v>
+      </c>
+      <c r="C14" s="1">
+        <v>17888</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4921</v>
+      </c>
+      <c r="E14" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>597</v>
+      </c>
+      <c r="C15" s="1">
+        <v>10035</v>
+      </c>
+      <c r="D15" s="1">
+        <v>10067</v>
+      </c>
+      <c r="E15" s="1">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1">
+        <v>16586</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1">
+        <v>14122</v>
+      </c>
+      <c r="D17" s="1">
+        <v>738</v>
+      </c>
+      <c r="E17" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>129</v>
+      </c>
+      <c r="C18" s="1">
+        <v>14070</v>
+      </c>
+      <c r="D18" s="1">
+        <v>112</v>
+      </c>
+      <c r="E18" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="1">
+        <v>26</v>
+      </c>
+      <c r="C19" s="1">
+        <v>8040</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>8615</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="1">
+        <v>809</v>
+      </c>
+      <c r="C21" s="1">
+        <v>6541</v>
+      </c>
+      <c r="D21" s="1">
+        <v>911</v>
+      </c>
+      <c r="E21" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="1">
+        <v>28</v>
+      </c>
+      <c r="C22" s="1">
+        <v>5230</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1097</v>
+      </c>
+      <c r="E22" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>6069</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="1">
+        <v>26</v>
+      </c>
+      <c r="C24" s="1">
+        <v>5133</v>
+      </c>
+      <c r="D24" s="1">
+        <v>218</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1">
+        <v>4610</v>
+      </c>
+      <c r="D25" s="1">
+        <v>115</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1478</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1204</v>
+      </c>
+      <c r="D26" s="1">
+        <v>13</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2528</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="1">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2500</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="1">
+        <v>3</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1216</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1155</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="1">
+        <v>916</v>
+      </c>
+      <c r="C32" s="1">
+        <v>13</v>
+      </c>
+      <c r="D32" s="1">
+        <v>162</v>
+      </c>
+      <c r="E32" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="1">
+        <v>0</v>
+      </c>
+      <c r="C33" s="1">
+        <v>969</v>
+      </c>
+      <c r="D33" s="1">
+        <v>19</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0</v>
+      </c>
+      <c r="C34" s="1">
+        <v>950</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="1">
+        <v>846</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="1">
+        <v>0</v>
+      </c>
+      <c r="C36" s="1">
+        <v>693</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" s="1">
+        <v>0</v>
+      </c>
+      <c r="C37" s="1">
+        <v>668</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1">
+        <v>74</v>
+      </c>
+      <c r="D38" s="1">
+        <v>591</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="1">
+        <v>121</v>
+      </c>
+      <c r="C39" s="1">
+        <v>144</v>
+      </c>
+      <c r="D39" s="1">
+        <v>213</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="1">
+        <v>0</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="1">
+        <v>0</v>
+      </c>
+      <c r="C41" s="1">
+        <v>17</v>
+      </c>
+      <c r="D41" s="1">
+        <v>351</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="1">
+        <v>0</v>
+      </c>
+      <c r="C42" s="1">
+        <v>332</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="1">
+        <v>0</v>
+      </c>
+      <c r="C43" s="1">
+        <v>210</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="1">
+        <v>0</v>
+      </c>
+      <c r="C44" s="1">
+        <v>63</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="1">
+        <v>37</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="1">
+        <v>0</v>
+      </c>
+      <c r="C46" s="1">
+        <v>28</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="1">
+        <v>24</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="1">
+        <v>18</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B40C8F7-1818-4E34-84A1-822694B55E8A}">
   <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -1738,7 +2571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE4528B-A567-469E-A6B5-0B3A45ED1A30}">
   <dimension ref="A1:U24"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -3219,12 +4052,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x0101000CCC32A541702F46A6CCB3BF85EDE9DB" ma:contentTypeVersion="12" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="42f5c27c5380a6d71c815158e2fdbf00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ee96044a-9bdd-49f6-b340-e6287396927a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8645e67c909ebaefdf7ac0e60ee83224" ns3:_="">
     <xsd:import namespace="ee96044a-9bdd-49f6-b340-e6287396927a"/>
@@ -3418,6 +4245,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8C312A1-39B6-41C3-8F19-F954E9608916}">
   <ds:schemaRefs>
@@ -3427,22 +4260,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA1960AE-9D49-40EB-BE78-445A254B68D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="ee96044a-9bdd-49f6-b340-e6287396927a"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2540BB-83D7-4902-AD1E-AF75136F2F44}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3458,4 +4275,20 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA1960AE-9D49-40EB-BE78-445A254B68D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="ee96044a-9bdd-49f6-b340-e6287396927a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>